--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123498361</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123498361</v>
       </c>
       <c r="B2" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123498361</v>
       </c>
       <c r="B2" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,103 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129468537</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95946</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Valås, Hallandsleden, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>329185</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6381610</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Wållberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Wållberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>129468537</v>
       </c>
       <c r="B4" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>129468537</v>
       </c>
       <c r="B4" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>129468537</v>
       </c>
       <c r="B4" t="n">
-        <v>95952</v>
+        <v>95960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>129468537</v>
       </c>
       <c r="B4" t="n">
-        <v>95960</v>
+        <v>95963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>129468537</v>
       </c>
       <c r="B4" t="n">
-        <v>95963</v>
+        <v>95992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>129468537</v>
       </c>
       <c r="B4" t="n">
-        <v>95992</v>
+        <v>96004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>129468537</v>
       </c>
       <c r="B4" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>129468537</v>
       </c>
       <c r="B4" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>129468537</v>
       </c>
       <c r="B4" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>129468537</v>
       </c>
       <c r="B4" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -675,52 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123498361</v>
+        <v>129468537</v>
       </c>
       <c r="B2" t="n">
-        <v>57519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valås, Hallandsleden, Hl</t>
@@ -757,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124576915</v>
+        <v>123498361</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,33 +783,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -871,22 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,35 +881,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129468537</v>
+        <v>124576915</v>
       </c>
       <c r="B4" t="n">
-        <v>96016</v>
+        <v>58238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valås, Hallandsleden, Hl</t>
@@ -978,12 +958,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 58-2025 artfynd.xlsx
+++ b/artfynd/A 58-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129468537</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123498361</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124576915</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>